--- a/events/Rio_2016_OG/Rio_2016_OG_Results.xlsx
+++ b/events/Rio_2016_OG/Rio_2016_OG_Results.xlsx
@@ -42060,7 +42060,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>da CONCEICAO TRISTE Buly</t>
+          <t>Buly</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>da CONCEICAO TRISTE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -42077,7 +42082,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>de JONGE Mark</t>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>de JONGE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -42094,7 +42104,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>de SOUZA SILVA Erlon</t>
+          <t>Erlon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>de SOUZA SILVA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -42111,7 +42126,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>de TORRES Pablo</t>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>de TORRES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -42128,7 +42148,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>van KOEVERDEN Adam</t>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>van KOEVERDEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/events/Rio_2016_OG/Rio_2016_OG_Results.xlsx
+++ b/events/Rio_2016_OG/Rio_2016_OG_Results.xlsx
@@ -1227,6 +1227,11 @@
           <t>+3.011</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2132,6 +2137,11 @@
           <t>+3.743</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3747,6 +3757,11 @@
           <t>+0.860</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5667,6 +5682,11 @@
           <t>+1.954</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6347,6 +6367,11 @@
           <t>3:58.259</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7452,6 +7477,11 @@
           <t>1:42.285</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8597,6 +8627,11 @@
           <t>+0.864</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10582,6 +10617,11 @@
           <t>3:34.833</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11910,6 +11950,11 @@
           <t>+4.037</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13159,6 +13204,11 @@
           <t>+3.280</t>
         </is>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -13797,6 +13847,11 @@
           <t>+0.532</t>
         </is>
       </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15207,6 +15262,11 @@
           <t>+1.916</t>
         </is>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15932,6 +15992,11 @@
           <t>43679</t>
         </is>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -16142,6 +16207,11 @@
           <t>+7.721</t>
         </is>
       </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>42171</t>
@@ -17122,6 +17192,11 @@
           <t>+0.163</t>
         </is>
       </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17957,6 +18032,11 @@
           <t>36228</t>
         </is>
       </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -18622,6 +18702,11 @@
           <t>47312</t>
         </is>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -19312,6 +19397,11 @@
           <t>+0.539</t>
         </is>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -20602,6 +20692,11 @@
           <t>3:16.635</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S288" t="inlineStr">
         <is>
           <t>42171</t>
@@ -21267,6 +21362,11 @@
           <t>43679</t>
         </is>
       </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -22292,6 +22392,11 @@
           <t>36228</t>
         </is>
       </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -22512,6 +22617,11 @@
           <t>47312</t>
         </is>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -23092,6 +23202,11 @@
           <t>1:55.641</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -24534,6 +24649,11 @@
           <t>43679</t>
         </is>
       </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -24981,6 +25101,11 @@
           <t>+1.812</t>
         </is>
       </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S350" t="inlineStr">
         <is>
           <t>42171</t>
@@ -25716,6 +25841,11 @@
           <t>+0.628</t>
         </is>
       </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -26637,6 +26767,11 @@
           <t>47312</t>
         </is>
       </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -27012,6 +27147,11 @@
           <t>36228</t>
         </is>
       </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -28318,6 +28458,11 @@
           <t>+1.980</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -28936,6 +29081,11 @@
           <t>+0.866</t>
         </is>
       </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -29416,6 +29566,11 @@
           <t>+0.923</t>
         </is>
       </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -29551,6 +29706,11 @@
           <t>+1.239</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>43681</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -30316,6 +30476,16 @@
           <t>+9.836</t>
         </is>
       </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -30976,6 +31146,16 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -31286,6 +31466,11 @@
           <t>+6.533</t>
         </is>
       </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
       <c r="S438" t="inlineStr">
         <is>
           <t>35813</t>
@@ -32266,6 +32451,11 @@
           <t>+2.830</t>
         </is>
       </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S450" t="inlineStr">
         <is>
           <t>61242</t>
@@ -32526,6 +32716,11 @@
           <t>42769</t>
         </is>
       </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -32936,6 +33131,11 @@
           <t>36150</t>
         </is>
       </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="U458" t="inlineStr">
         <is>
           <t>36152</t>
@@ -33676,6 +33876,11 @@
           <t>+1.491</t>
         </is>
       </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -33741,6 +33946,11 @@
           <t>+1.860</t>
         </is>
       </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -34801,6 +35011,16 @@
           <t>+1.935</t>
         </is>
       </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -35671,6 +35891,11 @@
           <t>+1.544</t>
         </is>
       </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
       <c r="S495" t="inlineStr">
         <is>
           <t>35813</t>
@@ -35981,6 +36206,11 @@
           <t>2:58.222</t>
         </is>
       </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S499" t="inlineStr">
         <is>
           <t>61242</t>
@@ -36741,6 +36971,11 @@
           <t>36150</t>
         </is>
       </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="U508" t="inlineStr">
         <is>
           <t>36152</t>
@@ -36911,6 +37146,11 @@
           <t>42769</t>
         </is>
       </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -37117,6 +37357,11 @@
           <t>+0.094</t>
         </is>
       </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -37328,6 +37573,11 @@
           <t>+0.407</t>
         </is>
       </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -38639,6 +38889,16 @@
           <t>+2.864</t>
         </is>
       </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -39608,6 +39868,16 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -39931,6 +40201,11 @@
           <t>+5.561</t>
         </is>
       </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
       <c r="S550" t="inlineStr">
         <is>
           <t>35813</t>
@@ -40089,6 +40364,11 @@
           <t>42769</t>
         </is>
       </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -40221,6 +40501,11 @@
           <t>36150</t>
         </is>
       </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="U554" t="inlineStr">
         <is>
           <t>36152</t>
@@ -40762,6 +41047,11 @@
           <t>+4.588</t>
         </is>
       </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S561" t="inlineStr">
         <is>
           <t>61242</t>
@@ -41873,6 +42163,11 @@
       <c r="Q576" t="inlineStr">
         <is>
           <t>+1.016</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>42411</t>
         </is>
       </c>
     </row>
@@ -42027,7 +42322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D217"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46804,6 +47099,314 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ANOSHKIN</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Ilya</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>PERVUKHIN</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>36222</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>WALKER</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SCHOFIELD</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Maryna</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>LITVINCHUK</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>DE CESARE</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Reiniel</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TORRES RIBEAUX</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>43681</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Fidel A</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>VARGAS DUANY</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Gilvan</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>BITTENCOURT RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>47712</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Evgenii</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>LUKANTSOV</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
